--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>700_米酒果_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010201015105510100</v>
+        <v>010201015105510105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,86 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>641_绿枫叶_maple leaf_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>334_狗尾草_puppy tail grass_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>387_洋甘菊_Chamomile_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>558_油画小菊_Helenium_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +658,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010201015105510105</v>
+        <v>01020101510551010510510101030205100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -475,7 +475,7 @@
     </row>
     <row r="6">
       <c r="C6" t="str">
-        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+        <v>571_大飞燕浅紫_undefined_undefined_1bunch</v>
       </c>
       <c r="F6" t="str">
         <v>10</v>
@@ -600,10 +600,96 @@
       <c r="C21" t="str">
         <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>82_非洲菊绿 绿扣子_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>3</v>
+      </c>
+      <c r="C23" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F23" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>18_波浪黄洋桔梗_Wavy Yellow Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v>696_百合笑脸_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>695_百合虎皮_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>859_喷色小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F30" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -658,7 +744,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01020101510551010510510101030205100</v>
+        <v>0102010151055101051051010103020510551555551010150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -686,10 +686,96 @@
       <c r="C31" t="str">
         <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>4</v>
+      </c>
+      <c r="C33" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>5</v>
+      </c>
+      <c r="C38" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -744,7 +830,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0102010151055101051051010103020510551555551010150</v>
+        <v>010201015105510105105101010302051055155555101015510121510310811110</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -772,6 +772,9 @@
       <c r="C41" t="str">
         <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -830,7 +833,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010201015105510105105101010302051055155555101015510121510310811110</v>
+        <v>010201015105510105105101010302051055155555101015510121510310811118</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -776,9 +776,89 @@
         <v>8</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>6</v>
+      </c>
+      <c r="C44" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>157_流沙_Quicksand_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -833,7 +913,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010201015105510105105101010302051055155555101015510121510310811118</v>
+        <v>0102010151055101051051010103020510551555551010155101215103108111184104881064100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -855,6 +855,9 @@
       <c r="C51" t="str">
         <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
       </c>
+      <c r="F51" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -913,7 +916,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0102010151055101051051010103020510551555551010155101215103108111184104881064100</v>
+        <v>0102010151055101051051010103020510551555551010155101215103108111184104881064105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -859,9 +859,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>7</v>
+      </c>
+      <c r="C53" t="str">
+        <v>256_奇迹女神_Miracle Goddess_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F59" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
+      </c>
+      <c r="F60" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>80_冰清玉洁_undefined_Gerbera L._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -916,7 +996,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0102010151055101051051010103020510551555551010155101215103108111184104881064105</v>
+        <v>010201015105510105105101010302051055155555101015510121510310811118410488106410556110851010100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -938,6 +938,9 @@
       <c r="C61" t="str">
         <v>80_冰清玉洁_undefined_Gerbera L._20stems</v>
       </c>
+      <c r="F61" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -996,7 +999,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010201015105510105105101010302051055155555101015510121510310811118410488106410556110851010100</v>
+        <v>0102010151055101051051010103020510551555551010155101215103108111184104881064105561108510101010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -942,9 +942,95 @@
         <v>10</v>
       </c>
     </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>77_珍爱mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F62" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v>79_福娃_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F63" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>8</v>
+      </c>
+      <c r="C64" t="str">
+        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
+      </c>
+      <c r="F64" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>143_黑巴克_Black Baccara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F65" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F66" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F67" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>9</v>
+      </c>
+      <c r="C68" t="str">
+        <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F68" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>788_国产直葱白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F69" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>415_百子莲蓝_Agapanthus_undefined_1bunch</v>
+      </c>
+      <c r="F70" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>769_菟葵绿铃铛_undefined_undefined_undefinedundefined</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -999,7 +1085,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0102010151055101051051010103020510551555551010155101215103108111184104881064105561108510101010</v>
+        <v>0102010151055101051051010103020510551555551010155101215103108111184104881064105561108510101010101040101010101050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -1023,9 +1023,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
-      <c r="C71" t="str">
-        <v>769_菟葵绿铃铛_undefined_undefined_undefinedundefined</v>
+    <row r="71" xml:space="preserve">
+      <c r="C71" t="str" xml:space="preserve">
+        <v xml:space="preserve">386_菟葵绿粉 
+green_undefined_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -1028,6 +1028,9 @@
         <v xml:space="preserve">386_菟葵绿粉 
 green_undefined_undefined_1bunch</v>
       </c>
+      <c r="F71" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1086,7 +1089,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0102010151055101051051010103020510551555551010155101215103108111184104881064105561108510101010101040101010101050</v>
+        <v>0102010151055101051051010103020510551555551010155101215103108111184104881064105561108510101010101040101010101055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L79"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1032,9 +1032,79 @@
         <v>5</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>10</v>
+      </c>
+      <c r="C72" t="str">
+        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
+      </c>
+      <c r="F72" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>43_拉丝红_Spider Red_Gerbera L._20stems</v>
+      </c>
+      <c r="F73" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F74" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F75" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>11</v>
+      </c>
+      <c r="C76" t="str">
+        <v>70_朝霞mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F76" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" t="str">
+        <v>44_拉丝粉_Spider Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F77" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F78" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F79" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L79"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1089,7 +1159,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0102010151055101051051010103020510551555551010155101215103108111184104881064105561108510101010101040101010101055</v>
+        <v>01020101510551010510510101030205105515555510101551012151031081111841048810641055611085101010101010401010101010551010101010355</v>
       </c>
     </row>
   </sheetData>
